--- a/outputs/monitor_xlsx/20260120.xlsx
+++ b/outputs/monitor_xlsx/20260120.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1113,40 +1116,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1201,12 +1199,7 @@
       <c r="O4" t="n">
         <v>1.77</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1244,12 +1237,7 @@
       <c r="N5" t="n">
         <v>-20248</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1307,12 +1295,7 @@
       <c r="O6" t="n">
         <v>10.68</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1370,12 +1353,7 @@
       <c r="O7" t="n">
         <v>5.02</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1433,12 +1411,7 @@
       <c r="O8" t="n">
         <v>3.08</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1496,12 +1469,7 @@
       <c r="O9" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1559,12 +1527,7 @@
       <c r="O10" t="n">
         <v>-0.06</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1622,12 +1585,7 @@
       <c r="O11" t="n">
         <v>-1.48</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1685,12 +1643,7 @@
       <c r="O12" t="n">
         <v>-2.46</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1748,12 +1701,7 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1811,12 +1759,7 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1874,12 +1817,7 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1934,12 +1872,7 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1997,12 +1930,7 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2057,12 +1985,7 @@
       <c r="O18" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2120,12 +2043,7 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2180,12 +2098,7 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/outputs/monitor_xlsx/20260120.xlsx
+++ b/outputs/monitor_xlsx/20260120.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1158,7 +1155,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1172,17 +1169,20 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>111046</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-47126</v>
       </c>
       <c r="H4" t="n">
-        <v>-73021</v>
+        <v>-103273</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-6994</v>
+        <v>-10016</v>
       </c>
       <c r="K4" t="n">
         <v>22419</v>
@@ -1191,13 +1191,13 @@
         <v>7890</v>
       </c>
       <c r="M4" t="n">
-        <v>38979</v>
+        <v>38704</v>
       </c>
       <c r="N4" t="n">
         <v>-3924500</v>
       </c>
       <c r="O4" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1259,26 +1259,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1005</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>4.36</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>8949</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1305</v>
       </c>
       <c r="H6" t="n">
-        <v>2736</v>
+        <v>3846</v>
       </c>
       <c r="I6" t="n">
         <v>64</v>
       </c>
       <c r="J6" t="n">
-        <v>1366</v>
+        <v>1140</v>
       </c>
       <c r="K6" t="n">
         <v>138</v>
@@ -1287,13 +1287,13 @@
         <v>3060</v>
       </c>
       <c r="M6" t="n">
-        <v>16878</v>
+        <v>16408</v>
       </c>
       <c r="N6" t="n">
         <v>-78528</v>
       </c>
       <c r="O6" t="n">
-        <v>10.68</v>
+        <v>14.74</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1317,26 +1317,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1130</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>0.89</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>7555</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>305</v>
       </c>
       <c r="H7" t="n">
-        <v>4819</v>
+        <v>5659</v>
       </c>
       <c r="I7" t="n">
         <v>147</v>
       </c>
       <c r="J7" t="n">
-        <v>341</v>
+        <v>686</v>
       </c>
       <c r="K7" t="n">
         <v>177</v>
@@ -1345,13 +1345,13 @@
         <v>8340</v>
       </c>
       <c r="M7" t="n">
-        <v>40133</v>
+        <v>41180</v>
       </c>
       <c r="N7" t="n">
         <v>-648569</v>
       </c>
       <c r="O7" t="n">
-        <v>5.02</v>
+        <v>6.05</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1375,26 +1375,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1775</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0.85</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>32687</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-5392</v>
       </c>
       <c r="H8" t="n">
-        <v>-17193</v>
+        <v>-19503</v>
       </c>
       <c r="I8" t="n">
         <v>-22</v>
       </c>
       <c r="J8" t="n">
-        <v>1349</v>
+        <v>1462</v>
       </c>
       <c r="K8" t="n">
         <v>1495</v>
@@ -1403,13 +1403,13 @@
         <v>20722</v>
       </c>
       <c r="M8" t="n">
-        <v>108919</v>
+        <v>107401</v>
       </c>
       <c r="N8" t="n">
         <v>-6482715</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1491,26 +1491,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>1615</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>2.22</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>2517</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1248</v>
       </c>
       <c r="H10" t="n">
-        <v>458</v>
+        <v>1058</v>
       </c>
       <c r="I10" t="n">
         <v>-182</v>
       </c>
       <c r="J10" t="n">
-        <v>-910</v>
+        <v>-1062</v>
       </c>
       <c r="K10" t="n">
         <v>75</v>
@@ -1519,13 +1519,13 @@
         <v>2371</v>
       </c>
       <c r="M10" t="n">
-        <v>13228</v>
+        <v>12838</v>
       </c>
       <c r="N10" t="n">
         <v>-89500</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06</v>
+        <v>0.83</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1607,26 +1607,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>1270</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>2.83</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>3660</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>-535</v>
       </c>
       <c r="H12" t="n">
-        <v>-908</v>
+        <v>-747</v>
       </c>
       <c r="I12" t="n">
         <v>68</v>
       </c>
       <c r="J12" t="n">
-        <v>-339</v>
+        <v>-427</v>
       </c>
       <c r="K12" t="n">
         <v>117</v>
@@ -1635,13 +1635,13 @@
         <v>5393</v>
       </c>
       <c r="M12" t="n">
-        <v>27133</v>
+        <v>27028</v>
       </c>
       <c r="N12" t="n">
         <v>-19167</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.46</v>
+        <v>-4.15</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1665,26 +1665,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1365</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9343</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1258</v>
       </c>
       <c r="H13" t="n">
-        <v>-1603</v>
+        <v>178</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>444</v>
+        <v>204</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1693,7 +1693,7 @@
         <v>-224</v>
       </c>
       <c r="M13" t="n">
-        <v>570</v>
+        <v>-54</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1839,23 +1839,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>400</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>-4.42</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7565</v>
+      <c r="D16" s="6" t="n">
+        <v>586</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-314</v>
       </c>
       <c r="H16" t="n">
-        <v>341</v>
+        <v>-1014</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-3758</v>
+        <v>-1626</v>
       </c>
       <c r="K16" t="n">
         <v>365</v>
@@ -1864,7 +1867,7 @@
         <v>2239</v>
       </c>
       <c r="M16" t="n">
-        <v>-3103</v>
+        <v>-250</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2002,46 +2005,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
         <v>1185</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="E19" s="6" t="n">
         <v>1.72</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>3573</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="G19" s="7" t="n">
         <v>907</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="H19" t="n">
         <v>1781</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>-278</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>-416</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>75</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>2515</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>13500</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>-140152</v>
       </c>
-      <c r="N19" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
+      <c r="O19" t="n">
+        <v>-2.16</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2168,46 +2171,46 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>962</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F22" s="6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G22" s="6" t="n">
         <v>-48</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>-114</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>-3</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>-11</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>18</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>-177</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+      <c r="O22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2261,6 +2264,218 @@
         <is>
           <t>偏空</t>
         </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>4547</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2993</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-570</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1398</v>
+      </c>
+      <c r="K24" t="n">
+        <v>120</v>
+      </c>
+      <c r="L24" t="n">
+        <v>858</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4682</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-106255</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>3740</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>969</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>73</v>
+      </c>
+      <c r="I25" t="n">
+        <v>163</v>
+      </c>
+      <c r="J25" t="n">
+        <v>191</v>
+      </c>
+      <c r="K25" t="n">
+        <v>13</v>
+      </c>
+      <c r="L25" t="n">
+        <v>412</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2364</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-8860</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7.66</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>194</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-260</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>14</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-30</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-16</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>7287</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>923</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-4107</v>
+      </c>
+      <c r="I27" t="n">
+        <v>60</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1188</v>
+      </c>
+      <c r="K27" t="n">
+        <v>47</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6780</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33765</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-21383</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
